--- a/paper/Tables/tablePilots.xlsx
+++ b/paper/Tables/tablePilots.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t># cases</t>
   </si>
@@ -148,6 +148,24 @@
   <si>
     <t xml:space="preserve">All workers approaching the information booth.
 </t>
+  </si>
+  <si>
+    <t>02/03/2016</t>
+  </si>
+  <si>
+    <t>27/05/2016</t>
+  </si>
+  <si>
+    <t>14/10/2016</t>
+  </si>
+  <si>
+    <t>10/02/2017</t>
+  </si>
+  <si>
+    <t>15/05/2017</t>
+  </si>
+  <si>
+    <t>17/08/2018</t>
   </si>
   <si>
     <t>02/03/2016</t>
@@ -623,10 +641,10 @@
 27/05/2016</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="72">
@@ -658,10 +676,10 @@
 10/02/2017</v>
       </c>
       <c r="K3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" ht="60.5" thickBot="true">
@@ -693,10 +711,10 @@
 17/08/2018</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" ht="15" thickTop="true"/>
